--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122851029</v>
+        <v>122850696</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558287</v>
+        <v>558333</v>
       </c>
       <c r="R2" t="n">
-        <v>6415378</v>
+        <v>6415302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +792,7 @@
         <v>122850848</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850538</v>
+        <v>122850920</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558333</v>
+        <v>558291</v>
       </c>
       <c r="R4" t="n">
-        <v>6415279</v>
+        <v>6415409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850816</v>
+        <v>122850715</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558317</v>
+        <v>558327</v>
       </c>
       <c r="R5" t="n">
-        <v>6415367</v>
+        <v>6415304</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122851058</v>
+        <v>122851054</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558281</v>
+        <v>558287</v>
       </c>
       <c r="R6" t="n">
-        <v>6415357</v>
+        <v>6415354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850740</v>
+        <v>122850882</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558324</v>
+        <v>558304</v>
       </c>
       <c r="R7" t="n">
-        <v>6415313</v>
+        <v>6415376</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122851076</v>
+        <v>122851065</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558271</v>
+        <v>558266</v>
       </c>
       <c r="R8" t="n">
-        <v>6415361</v>
+        <v>6415358</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851047</v>
+        <v>122850599</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558301</v>
+        <v>558331</v>
       </c>
       <c r="R9" t="n">
-        <v>6415402</v>
+        <v>6415292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850746</v>
+        <v>122850658</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,35 +1578,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558336</v>
+        <v>558326</v>
       </c>
       <c r="R10" t="n">
-        <v>6415318</v>
+        <v>6415300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850991</v>
+        <v>122851012</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1724,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558288</v>
+        <v>558276</v>
       </c>
       <c r="R11" t="n">
-        <v>6415391</v>
+        <v>6415383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850920</v>
+        <v>122851040</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558291</v>
+        <v>558287</v>
       </c>
       <c r="R12" t="n">
-        <v>6415409</v>
+        <v>6415363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1898,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850566</v>
+        <v>122850974</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1946,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558328</v>
+        <v>558285</v>
       </c>
       <c r="R13" t="n">
-        <v>6415288</v>
+        <v>6415397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2009,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850696</v>
+        <v>122850538</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,39 +2021,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,10 +2060,10 @@
         <v>558333</v>
       </c>
       <c r="R14" t="n">
-        <v>6415302</v>
+        <v>6415279</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,6 +2101,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850658</v>
+        <v>122850785</v>
       </c>
       <c r="B15" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,34 +2132,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558326</v>
+        <v>558330</v>
       </c>
       <c r="R15" t="n">
-        <v>6415300</v>
+        <v>6415337</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850785</v>
+        <v>122850566</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558330</v>
+        <v>558328</v>
       </c>
       <c r="R16" t="n">
-        <v>6415337</v>
+        <v>6415288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850599</v>
+        <v>122851076</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558331</v>
+        <v>558271</v>
       </c>
       <c r="R17" t="n">
-        <v>6415292</v>
+        <v>6415361</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851099</v>
+        <v>122850931</v>
       </c>
       <c r="B18" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2465,39 +2465,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2505,13 +2501,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558307</v>
+        <v>558298</v>
       </c>
       <c r="R18" t="n">
-        <v>6415333</v>
+        <v>6415413</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,6 +2545,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2567,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850931</v>
+        <v>122851029</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558298</v>
+        <v>558287</v>
       </c>
       <c r="R19" t="n">
-        <v>6415413</v>
+        <v>6415378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850918</v>
+        <v>122851099</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2690,35 +2687,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2726,13 +2727,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558314</v>
+        <v>558307</v>
       </c>
       <c r="R20" t="n">
-        <v>6415393</v>
+        <v>6415333</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2770,7 +2771,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850974</v>
+        <v>122850865</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558285</v>
+        <v>558306</v>
       </c>
       <c r="R21" t="n">
-        <v>6415397</v>
+        <v>6415378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851012</v>
+        <v>122851047</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558276</v>
+        <v>558301</v>
       </c>
       <c r="R22" t="n">
-        <v>6415383</v>
+        <v>6415402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851065</v>
+        <v>122850901</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558266</v>
+        <v>558311</v>
       </c>
       <c r="R23" t="n">
-        <v>6415358</v>
+        <v>6415391</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851040</v>
+        <v>122850746</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558287</v>
+        <v>558336</v>
       </c>
       <c r="R24" t="n">
-        <v>6415363</v>
+        <v>6415318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850901</v>
+        <v>122850913</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3281,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558311</v>
+        <v>558297</v>
       </c>
       <c r="R25" t="n">
-        <v>6415391</v>
+        <v>6415398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850882</v>
+        <v>122850991</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558304</v>
+        <v>558288</v>
       </c>
       <c r="R26" t="n">
-        <v>6415376</v>
+        <v>6415391</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850631</v>
+        <v>122851058</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558328</v>
+        <v>558281</v>
       </c>
       <c r="R27" t="n">
-        <v>6415300</v>
+        <v>6415357</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850865</v>
+        <v>122850918</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558306</v>
+        <v>558314</v>
       </c>
       <c r="R28" t="n">
-        <v>6415378</v>
+        <v>6415393</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850580</v>
+        <v>122850937</v>
       </c>
       <c r="B29" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3721,14 +3721,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558326</v>
+        <v>558285</v>
       </c>
       <c r="R29" t="n">
-        <v>6415304</v>
+        <v>6415400</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850937</v>
+        <v>122850800</v>
       </c>
       <c r="B30" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558285</v>
+        <v>558344</v>
       </c>
       <c r="R30" t="n">
-        <v>6415400</v>
+        <v>6415332</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850715</v>
+        <v>122850740</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558327</v>
+        <v>558324</v>
       </c>
       <c r="R31" t="n">
-        <v>6415304</v>
+        <v>6415313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850800</v>
+        <v>122850835</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558344</v>
+        <v>558314</v>
       </c>
       <c r="R32" t="n">
-        <v>6415332</v>
+        <v>6415377</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850913</v>
+        <v>122850580</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4165,14 +4165,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558297</v>
+        <v>558326</v>
       </c>
       <c r="R33" t="n">
-        <v>6415398</v>
+        <v>6415304</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851054</v>
+        <v>122850816</v>
       </c>
       <c r="B34" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558287</v>
+        <v>558317</v>
       </c>
       <c r="R34" t="n">
-        <v>6415354</v>
+        <v>6415367</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850835</v>
+        <v>122850631</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558314</v>
+        <v>558328</v>
       </c>
       <c r="R35" t="n">
-        <v>6415377</v>
+        <v>6415300</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850696</v>
+        <v>122850937</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558333</v>
+        <v>558285</v>
       </c>
       <c r="R2" t="n">
-        <v>6415302</v>
+        <v>6415400</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850848</v>
+        <v>122851040</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558303</v>
+        <v>558287</v>
       </c>
       <c r="R3" t="n">
-        <v>6415374</v>
+        <v>6415363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850920</v>
+        <v>122850746</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558291</v>
+        <v>558336</v>
       </c>
       <c r="R4" t="n">
-        <v>6415409</v>
+        <v>6415318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850715</v>
+        <v>122850658</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558327</v>
+        <v>558326</v>
       </c>
       <c r="R5" t="n">
-        <v>6415304</v>
+        <v>6415300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122851054</v>
+        <v>122851065</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1170,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558287</v>
+        <v>558266</v>
       </c>
       <c r="R6" t="n">
-        <v>6415354</v>
+        <v>6415358</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850882</v>
+        <v>122851058</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1281,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558304</v>
+        <v>558281</v>
       </c>
       <c r="R7" t="n">
-        <v>6415376</v>
+        <v>6415357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1340,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122851065</v>
+        <v>122850740</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1392,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558266</v>
+        <v>558324</v>
       </c>
       <c r="R8" t="n">
-        <v>6415358</v>
+        <v>6415313</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1451,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850599</v>
+        <v>122850920</v>
       </c>
       <c r="B9" t="n">
         <v>98355</v>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558331</v>
+        <v>558291</v>
       </c>
       <c r="R9" t="n">
-        <v>6415292</v>
+        <v>6415409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850658</v>
+        <v>122850599</v>
       </c>
       <c r="B10" t="n">
-        <v>92225</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,34 +1574,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1613,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558326</v>
+        <v>558331</v>
       </c>
       <c r="R10" t="n">
-        <v>6415300</v>
+        <v>6415292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1673,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122851012</v>
+        <v>122850580</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1720,14 +1717,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558276</v>
+        <v>558326</v>
       </c>
       <c r="R11" t="n">
-        <v>6415383</v>
+        <v>6415304</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122851040</v>
+        <v>122850816</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1835,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558287</v>
+        <v>558317</v>
       </c>
       <c r="R12" t="n">
-        <v>6415363</v>
+        <v>6415367</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1895,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850974</v>
+        <v>122850848</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1946,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558285</v>
+        <v>558303</v>
       </c>
       <c r="R13" t="n">
-        <v>6415397</v>
+        <v>6415374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2006,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850538</v>
+        <v>122850913</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2057,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558333</v>
+        <v>558297</v>
       </c>
       <c r="R14" t="n">
-        <v>6415279</v>
+        <v>6415398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850785</v>
+        <v>122850538</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2168,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558330</v>
+        <v>558333</v>
       </c>
       <c r="R15" t="n">
-        <v>6415337</v>
+        <v>6415279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850566</v>
+        <v>122851047</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2279,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558328</v>
+        <v>558301</v>
       </c>
       <c r="R16" t="n">
-        <v>6415288</v>
+        <v>6415402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2339,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851076</v>
+        <v>122850918</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2390,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558271</v>
+        <v>558314</v>
       </c>
       <c r="R17" t="n">
-        <v>6415361</v>
+        <v>6415393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2450,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850931</v>
+        <v>122850991</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2501,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558298</v>
+        <v>558288</v>
       </c>
       <c r="R18" t="n">
-        <v>6415413</v>
+        <v>6415391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851029</v>
+        <v>122851099</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,35 +2573,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2612,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558287</v>
+        <v>558307</v>
       </c>
       <c r="R19" t="n">
-        <v>6415378</v>
+        <v>6415333</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2656,7 +2657,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851099</v>
+        <v>122850882</v>
       </c>
       <c r="B20" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,39 +2687,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2727,13 +2723,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558307</v>
+        <v>558304</v>
       </c>
       <c r="R20" t="n">
-        <v>6415333</v>
+        <v>6415376</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,6 +2767,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2897,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851047</v>
+        <v>122850566</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -2948,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558301</v>
+        <v>558328</v>
       </c>
       <c r="R22" t="n">
-        <v>6415402</v>
+        <v>6415288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3008,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850901</v>
+        <v>122850974</v>
       </c>
       <c r="B23" t="n">
         <v>98355</v>
@@ -3059,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558311</v>
+        <v>558285</v>
       </c>
       <c r="R23" t="n">
-        <v>6415391</v>
+        <v>6415397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3122,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850746</v>
+        <v>122850835</v>
       </c>
       <c r="B24" t="n">
         <v>98355</v>
@@ -3170,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558336</v>
+        <v>558314</v>
       </c>
       <c r="R24" t="n">
-        <v>6415318</v>
+        <v>6415377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3230,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850913</v>
+        <v>122851076</v>
       </c>
       <c r="B25" t="n">
         <v>98355</v>
@@ -3281,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558297</v>
+        <v>558271</v>
       </c>
       <c r="R25" t="n">
-        <v>6415398</v>
+        <v>6415361</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850991</v>
+        <v>122850785</v>
       </c>
       <c r="B26" t="n">
         <v>98355</v>
@@ -3392,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558288</v>
+        <v>558330</v>
       </c>
       <c r="R26" t="n">
-        <v>6415391</v>
+        <v>6415337</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3452,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851058</v>
+        <v>122851012</v>
       </c>
       <c r="B27" t="n">
         <v>98355</v>
@@ -3503,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558281</v>
+        <v>558276</v>
       </c>
       <c r="R27" t="n">
-        <v>6415357</v>
+        <v>6415383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,7 +3563,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850918</v>
+        <v>122850800</v>
       </c>
       <c r="B28" t="n">
         <v>98355</v>
@@ -3614,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558314</v>
+        <v>558344</v>
       </c>
       <c r="R28" t="n">
-        <v>6415393</v>
+        <v>6415332</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,7 +3674,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850937</v>
+        <v>122850901</v>
       </c>
       <c r="B29" t="n">
         <v>98355</v>
@@ -3725,10 +3722,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558285</v>
+        <v>558311</v>
       </c>
       <c r="R29" t="n">
-        <v>6415400</v>
+        <v>6415391</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,7 +3785,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850800</v>
+        <v>122851054</v>
       </c>
       <c r="B30" t="n">
         <v>98355</v>
@@ -3836,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558344</v>
+        <v>558287</v>
       </c>
       <c r="R30" t="n">
-        <v>6415332</v>
+        <v>6415354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,7 +3896,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850740</v>
+        <v>122851029</v>
       </c>
       <c r="B31" t="n">
         <v>98355</v>
@@ -3947,10 +3944,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558324</v>
+        <v>558287</v>
       </c>
       <c r="R31" t="n">
-        <v>6415313</v>
+        <v>6415378</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,7 +4007,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850835</v>
+        <v>122850715</v>
       </c>
       <c r="B32" t="n">
         <v>98355</v>
@@ -4058,10 +4055,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558314</v>
+        <v>558327</v>
       </c>
       <c r="R32" t="n">
-        <v>6415377</v>
+        <v>6415304</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,7 +4118,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850580</v>
+        <v>122850631</v>
       </c>
       <c r="B33" t="n">
         <v>98355</v>
@@ -4165,14 +4162,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558326</v>
+        <v>558328</v>
       </c>
       <c r="R33" t="n">
-        <v>6415304</v>
+        <v>6415300</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4229,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850816</v>
+        <v>122850931</v>
       </c>
       <c r="B34" t="n">
         <v>98355</v>
@@ -4280,10 +4277,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558317</v>
+        <v>558298</v>
       </c>
       <c r="R34" t="n">
-        <v>6415367</v>
+        <v>6415413</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4340,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850631</v>
+        <v>122850696</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4355,35 +4352,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4391,13 +4392,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558328</v>
+        <v>558333</v>
       </c>
       <c r="R35" t="n">
-        <v>6415300</v>
+        <v>6415302</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4435,7 +4436,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850937</v>
+        <v>122851058</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558285</v>
+        <v>558281</v>
       </c>
       <c r="R2" t="n">
-        <v>6415400</v>
+        <v>6415357</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122851040</v>
+        <v>122851012</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558287</v>
+        <v>558276</v>
       </c>
       <c r="R3" t="n">
-        <v>6415363</v>
+        <v>6415383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850746</v>
+        <v>122850931</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558336</v>
+        <v>558298</v>
       </c>
       <c r="R4" t="n">
-        <v>6415318</v>
+        <v>6415413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850658</v>
+        <v>122850974</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,34 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558326</v>
+        <v>558285</v>
       </c>
       <c r="R5" t="n">
-        <v>6415300</v>
+        <v>6415397</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122851065</v>
+        <v>122851054</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558266</v>
+        <v>558287</v>
       </c>
       <c r="R6" t="n">
-        <v>6415358</v>
+        <v>6415354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122851058</v>
+        <v>122851065</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558281</v>
+        <v>558266</v>
       </c>
       <c r="R7" t="n">
-        <v>6415357</v>
+        <v>6415358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850740</v>
+        <v>122850848</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558324</v>
+        <v>558303</v>
       </c>
       <c r="R8" t="n">
-        <v>6415313</v>
+        <v>6415374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850920</v>
+        <v>122850746</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558291</v>
+        <v>558336</v>
       </c>
       <c r="R9" t="n">
-        <v>6415409</v>
+        <v>6415318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850599</v>
+        <v>122850920</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558331</v>
+        <v>558291</v>
       </c>
       <c r="R10" t="n">
-        <v>6415292</v>
+        <v>6415409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850580</v>
+        <v>122850696</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1685,49 +1686,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558326</v>
+        <v>558333</v>
       </c>
       <c r="R11" t="n">
-        <v>6415304</v>
+        <v>6415302</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,7 +1770,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1784,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850816</v>
+        <v>122850913</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558317</v>
+        <v>558297</v>
       </c>
       <c r="R12" t="n">
-        <v>6415367</v>
+        <v>6415398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850848</v>
+        <v>122851076</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558303</v>
+        <v>558271</v>
       </c>
       <c r="R13" t="n">
-        <v>6415374</v>
+        <v>6415361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850913</v>
+        <v>122850882</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558297</v>
+        <v>558304</v>
       </c>
       <c r="R14" t="n">
-        <v>6415398</v>
+        <v>6415376</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850538</v>
+        <v>122851029</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R15" t="n">
-        <v>6415279</v>
+        <v>6415378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851047</v>
+        <v>122850865</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558301</v>
+        <v>558306</v>
       </c>
       <c r="R16" t="n">
-        <v>6415402</v>
+        <v>6415378</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2346,7 @@
         <v>122850918</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850991</v>
+        <v>122850631</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558288</v>
+        <v>558328</v>
       </c>
       <c r="R18" t="n">
-        <v>6415391</v>
+        <v>6415300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851099</v>
+        <v>122850816</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,39 +2577,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558307</v>
+        <v>558317</v>
       </c>
       <c r="R19" t="n">
-        <v>6415333</v>
+        <v>6415367</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,6 +2657,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2675,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850882</v>
+        <v>122851047</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558304</v>
+        <v>558301</v>
       </c>
       <c r="R20" t="n">
-        <v>6415376</v>
+        <v>6415402</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850865</v>
+        <v>122850937</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558306</v>
+        <v>558285</v>
       </c>
       <c r="R21" t="n">
-        <v>6415378</v>
+        <v>6415400</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850566</v>
+        <v>122850599</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558328</v>
+        <v>558331</v>
       </c>
       <c r="R22" t="n">
-        <v>6415288</v>
+        <v>6415292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850974</v>
+        <v>122850715</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558285</v>
+        <v>558327</v>
       </c>
       <c r="R23" t="n">
-        <v>6415397</v>
+        <v>6415304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850835</v>
+        <v>122850658</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3131,35 +3132,34 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558314</v>
+        <v>558326</v>
       </c>
       <c r="R24" t="n">
-        <v>6415377</v>
+        <v>6415300</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851076</v>
+        <v>122851099</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,35 +3242,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3278,13 +3282,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558271</v>
+        <v>558307</v>
       </c>
       <c r="R25" t="n">
-        <v>6415361</v>
+        <v>6415333</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3322,7 +3326,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850785</v>
+        <v>122851040</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,10 +3392,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558330</v>
+        <v>558287</v>
       </c>
       <c r="R26" t="n">
-        <v>6415337</v>
+        <v>6415363</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851012</v>
+        <v>122850991</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558276</v>
+        <v>558288</v>
       </c>
       <c r="R27" t="n">
-        <v>6415383</v>
+        <v>6415391</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,7 +3569,7 @@
         <v>122850800</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3677,7 +3680,7 @@
         <v>122850901</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851054</v>
+        <v>122850785</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558287</v>
+        <v>558330</v>
       </c>
       <c r="R30" t="n">
-        <v>6415354</v>
+        <v>6415337</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851029</v>
+        <v>122850538</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558287</v>
+        <v>558333</v>
       </c>
       <c r="R31" t="n">
-        <v>6415378</v>
+        <v>6415279</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850715</v>
+        <v>122850580</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,11 +4054,11 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558327</v>
+        <v>558326</v>
       </c>
       <c r="R32" t="n">
         <v>6415304</v>
@@ -4118,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850631</v>
+        <v>122850566</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,7 +4172,7 @@
         <v>558328</v>
       </c>
       <c r="R33" t="n">
-        <v>6415300</v>
+        <v>6415288</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4229,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850931</v>
+        <v>122850835</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4277,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558298</v>
+        <v>558314</v>
       </c>
       <c r="R34" t="n">
-        <v>6415413</v>
+        <v>6415377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4340,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850696</v>
+        <v>122850740</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4352,39 +4355,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4392,13 +4391,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558333</v>
+        <v>558324</v>
       </c>
       <c r="R35" t="n">
-        <v>6415302</v>
+        <v>6415313</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4436,6 +4435,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122851058</v>
+        <v>122850913</v>
       </c>
       <c r="B2" t="n">
         <v>98357</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558281</v>
+        <v>558297</v>
       </c>
       <c r="R2" t="n">
-        <v>6415357</v>
+        <v>6415398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122851012</v>
+        <v>122851099</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558276</v>
+        <v>558307</v>
       </c>
       <c r="R3" t="n">
-        <v>6415383</v>
+        <v>6415333</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850931</v>
+        <v>122850785</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558298</v>
+        <v>558330</v>
       </c>
       <c r="R4" t="n">
-        <v>6415413</v>
+        <v>6415337</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850974</v>
+        <v>122850599</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558285</v>
+        <v>558331</v>
       </c>
       <c r="R5" t="n">
-        <v>6415397</v>
+        <v>6415292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122851054</v>
+        <v>122850715</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558287</v>
+        <v>558327</v>
       </c>
       <c r="R6" t="n">
-        <v>6415354</v>
+        <v>6415304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122851065</v>
+        <v>122851076</v>
       </c>
       <c r="B7" t="n">
         <v>98357</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558266</v>
+        <v>558271</v>
       </c>
       <c r="R7" t="n">
-        <v>6415358</v>
+        <v>6415361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850848</v>
+        <v>122850931</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558303</v>
+        <v>558298</v>
       </c>
       <c r="R8" t="n">
-        <v>6415374</v>
+        <v>6415413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850746</v>
+        <v>122850816</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558336</v>
+        <v>558317</v>
       </c>
       <c r="R9" t="n">
-        <v>6415318</v>
+        <v>6415367</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850920</v>
+        <v>122850901</v>
       </c>
       <c r="B10" t="n">
         <v>98357</v>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558291</v>
+        <v>558311</v>
       </c>
       <c r="R10" t="n">
-        <v>6415409</v>
+        <v>6415391</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850696</v>
+        <v>122850937</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,39 +1689,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1726,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558333</v>
+        <v>558285</v>
       </c>
       <c r="R11" t="n">
-        <v>6415302</v>
+        <v>6415400</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,6 +1769,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850913</v>
+        <v>122850746</v>
       </c>
       <c r="B12" t="n">
         <v>98357</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558297</v>
+        <v>558336</v>
       </c>
       <c r="R12" t="n">
-        <v>6415398</v>
+        <v>6415318</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122851076</v>
+        <v>122850696</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1911,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1947,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558271</v>
+        <v>558333</v>
       </c>
       <c r="R13" t="n">
-        <v>6415361</v>
+        <v>6415302</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2010,7 +2013,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850882</v>
+        <v>122850918</v>
       </c>
       <c r="B14" t="n">
         <v>98357</v>
@@ -2058,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558304</v>
+        <v>558314</v>
       </c>
       <c r="R14" t="n">
-        <v>6415376</v>
+        <v>6415393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122851029</v>
+        <v>122850538</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558287</v>
+        <v>558333</v>
       </c>
       <c r="R15" t="n">
-        <v>6415378</v>
+        <v>6415279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2235,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850865</v>
+        <v>122851058</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2280,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558306</v>
+        <v>558281</v>
       </c>
       <c r="R16" t="n">
-        <v>6415378</v>
+        <v>6415357</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,7 +2346,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850918</v>
+        <v>122850865</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2391,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558314</v>
+        <v>558306</v>
       </c>
       <c r="R17" t="n">
-        <v>6415393</v>
+        <v>6415378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2457,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850631</v>
+        <v>122851065</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2502,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558328</v>
+        <v>558266</v>
       </c>
       <c r="R18" t="n">
-        <v>6415300</v>
+        <v>6415358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2568,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850816</v>
+        <v>122850631</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2613,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558317</v>
+        <v>558328</v>
       </c>
       <c r="R19" t="n">
-        <v>6415367</v>
+        <v>6415300</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2679,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851047</v>
+        <v>122850580</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -2720,14 +2723,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558301</v>
+        <v>558326</v>
       </c>
       <c r="R20" t="n">
-        <v>6415402</v>
+        <v>6415304</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2790,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850937</v>
+        <v>122850882</v>
       </c>
       <c r="B21" t="n">
         <v>98357</v>
@@ -2835,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558285</v>
+        <v>558304</v>
       </c>
       <c r="R21" t="n">
-        <v>6415400</v>
+        <v>6415376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2901,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850599</v>
+        <v>122851047</v>
       </c>
       <c r="B22" t="n">
         <v>98357</v>
@@ -2946,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558331</v>
+        <v>558301</v>
       </c>
       <c r="R22" t="n">
-        <v>6415292</v>
+        <v>6415402</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3012,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850715</v>
+        <v>122850566</v>
       </c>
       <c r="B23" t="n">
         <v>98357</v>
@@ -3057,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558327</v>
+        <v>558328</v>
       </c>
       <c r="R23" t="n">
-        <v>6415304</v>
+        <v>6415288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850658</v>
+        <v>122850848</v>
       </c>
       <c r="B24" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3132,34 +3135,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3167,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558326</v>
+        <v>558303</v>
       </c>
       <c r="R24" t="n">
-        <v>6415300</v>
+        <v>6415374</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851099</v>
+        <v>122850835</v>
       </c>
       <c r="B25" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,39 +3246,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3282,13 +3282,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558307</v>
+        <v>558314</v>
       </c>
       <c r="R25" t="n">
-        <v>6415333</v>
+        <v>6415377</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,6 +3326,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3344,7 +3345,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851040</v>
+        <v>122850740</v>
       </c>
       <c r="B26" t="n">
         <v>98357</v>
@@ -3392,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558287</v>
+        <v>558324</v>
       </c>
       <c r="R26" t="n">
-        <v>6415363</v>
+        <v>6415313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3456,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850991</v>
+        <v>122851040</v>
       </c>
       <c r="B27" t="n">
         <v>98357</v>
@@ -3503,10 +3504,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558288</v>
+        <v>558287</v>
       </c>
       <c r="R27" t="n">
-        <v>6415391</v>
+        <v>6415363</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850800</v>
+        <v>122850658</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3578,35 +3579,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558344</v>
+        <v>558326</v>
       </c>
       <c r="R28" t="n">
-        <v>6415332</v>
+        <v>6415300</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850901</v>
+        <v>122851029</v>
       </c>
       <c r="B29" t="n">
         <v>98357</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558311</v>
+        <v>558287</v>
       </c>
       <c r="R29" t="n">
-        <v>6415391</v>
+        <v>6415378</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,7 +3788,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850785</v>
+        <v>122850991</v>
       </c>
       <c r="B30" t="n">
         <v>98357</v>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558330</v>
+        <v>558288</v>
       </c>
       <c r="R30" t="n">
-        <v>6415337</v>
+        <v>6415391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850538</v>
+        <v>122851054</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R31" t="n">
-        <v>6415279</v>
+        <v>6415354</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850580</v>
+        <v>122850800</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -4054,14 +4054,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558326</v>
+        <v>558344</v>
       </c>
       <c r="R32" t="n">
-        <v>6415304</v>
+        <v>6415332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850566</v>
+        <v>122851012</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558328</v>
+        <v>558276</v>
       </c>
       <c r="R33" t="n">
-        <v>6415288</v>
+        <v>6415383</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850835</v>
+        <v>122850974</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558314</v>
+        <v>558285</v>
       </c>
       <c r="R34" t="n">
-        <v>6415377</v>
+        <v>6415397</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850740</v>
+        <v>122850920</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558324</v>
+        <v>558291</v>
       </c>
       <c r="R35" t="n">
-        <v>6415313</v>
+        <v>6415409</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850696</v>
+        <v>122850538</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,39 +1911,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1954,10 +1950,10 @@
         <v>558333</v>
       </c>
       <c r="R13" t="n">
-        <v>6415302</v>
+        <v>6415279</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1991,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850918</v>
+        <v>122850696</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2022,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558314</v>
+        <v>558333</v>
       </c>
       <c r="R14" t="n">
-        <v>6415393</v>
+        <v>6415302</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2105,7 +2106,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850538</v>
+        <v>122850918</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558333</v>
+        <v>558314</v>
       </c>
       <c r="R15" t="n">
-        <v>6415279</v>
+        <v>6415393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850658</v>
+        <v>122851029</v>
       </c>
       <c r="B28" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3579,34 +3579,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3614,10 +3615,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558326</v>
+        <v>558287</v>
       </c>
       <c r="R28" t="n">
-        <v>6415300</v>
+        <v>6415378</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,10 +3678,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851029</v>
+        <v>122850658</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3689,35 +3690,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558287</v>
+        <v>558326</v>
       </c>
       <c r="R29" t="n">
-        <v>6415378</v>
+        <v>6415300</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -1899,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850538</v>
+        <v>122850696</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,35 +1911,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1950,10 +1954,10 @@
         <v>558333</v>
       </c>
       <c r="R13" t="n">
-        <v>6415279</v>
+        <v>6415302</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850696</v>
+        <v>122850918</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,39 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2062,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558333</v>
+        <v>558314</v>
       </c>
       <c r="R14" t="n">
-        <v>6415302</v>
+        <v>6415393</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850918</v>
+        <v>122850538</v>
       </c>
       <c r="B15" t="n">
         <v>98357</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558314</v>
+        <v>558333</v>
       </c>
       <c r="R15" t="n">
-        <v>6415393</v>
+        <v>6415279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2901,7 +2901,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851047</v>
+        <v>122850566</v>
       </c>
       <c r="B22" t="n">
         <v>98357</v>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558301</v>
+        <v>558328</v>
       </c>
       <c r="R22" t="n">
-        <v>6415402</v>
+        <v>6415288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850566</v>
+        <v>122851047</v>
       </c>
       <c r="B23" t="n">
         <v>98357</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558328</v>
+        <v>558301</v>
       </c>
       <c r="R23" t="n">
-        <v>6415288</v>
+        <v>6415402</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850913</v>
+        <v>122850920</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558297</v>
+        <v>558291</v>
       </c>
       <c r="R2" t="n">
-        <v>6415398</v>
+        <v>6415409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122851099</v>
+        <v>122850991</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558307</v>
+        <v>558288</v>
       </c>
       <c r="R3" t="n">
-        <v>6415333</v>
+        <v>6415391</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850785</v>
+        <v>122850937</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558330</v>
+        <v>558285</v>
       </c>
       <c r="R4" t="n">
-        <v>6415337</v>
+        <v>6415400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850599</v>
+        <v>122850746</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558331</v>
+        <v>558336</v>
       </c>
       <c r="R5" t="n">
-        <v>6415292</v>
+        <v>6415318</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850715</v>
+        <v>122851029</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558327</v>
+        <v>558287</v>
       </c>
       <c r="R6" t="n">
-        <v>6415304</v>
+        <v>6415378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122851076</v>
+        <v>122850740</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558271</v>
+        <v>558324</v>
       </c>
       <c r="R7" t="n">
-        <v>6415361</v>
+        <v>6415313</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850931</v>
+        <v>122850865</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558298</v>
+        <v>558306</v>
       </c>
       <c r="R8" t="n">
-        <v>6415413</v>
+        <v>6415378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850816</v>
+        <v>122851076</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558317</v>
+        <v>558271</v>
       </c>
       <c r="R9" t="n">
-        <v>6415367</v>
+        <v>6415361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850901</v>
+        <v>122851058</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558311</v>
+        <v>558281</v>
       </c>
       <c r="R10" t="n">
-        <v>6415391</v>
+        <v>6415357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850937</v>
+        <v>122851054</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558285</v>
+        <v>558287</v>
       </c>
       <c r="R11" t="n">
-        <v>6415400</v>
+        <v>6415354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850746</v>
+        <v>122850599</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558336</v>
+        <v>558331</v>
       </c>
       <c r="R12" t="n">
-        <v>6415318</v>
+        <v>6415292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850696</v>
+        <v>122850913</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,39 +1908,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,13 +1944,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558333</v>
+        <v>558297</v>
       </c>
       <c r="R13" t="n">
-        <v>6415302</v>
+        <v>6415398</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1988,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850918</v>
+        <v>122850658</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>92233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,35 +2019,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2061,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558314</v>
+        <v>558326</v>
       </c>
       <c r="R14" t="n">
-        <v>6415393</v>
+        <v>6415300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850538</v>
+        <v>122851099</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2136,35 +2129,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2172,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558333</v>
+        <v>558307</v>
       </c>
       <c r="R15" t="n">
-        <v>6415279</v>
+        <v>6415333</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2216,7 +2213,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2235,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851058</v>
+        <v>122850538</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558281</v>
+        <v>558333</v>
       </c>
       <c r="R16" t="n">
-        <v>6415357</v>
+        <v>6415279</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850865</v>
+        <v>122851012</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558306</v>
+        <v>558276</v>
       </c>
       <c r="R17" t="n">
-        <v>6415378</v>
+        <v>6415383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851065</v>
+        <v>122850882</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558266</v>
+        <v>558304</v>
       </c>
       <c r="R18" t="n">
-        <v>6415358</v>
+        <v>6415376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850631</v>
+        <v>122850816</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2616,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558328</v>
+        <v>558317</v>
       </c>
       <c r="R19" t="n">
-        <v>6415300</v>
+        <v>6415367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850580</v>
+        <v>122850800</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,14 +2719,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558326</v>
+        <v>558344</v>
       </c>
       <c r="R20" t="n">
-        <v>6415304</v>
+        <v>6415332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850882</v>
+        <v>122850901</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,10 +2834,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558304</v>
+        <v>558311</v>
       </c>
       <c r="R21" t="n">
-        <v>6415376</v>
+        <v>6415391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850566</v>
+        <v>122850785</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2949,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558328</v>
+        <v>558330</v>
       </c>
       <c r="R22" t="n">
-        <v>6415288</v>
+        <v>6415337</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851047</v>
+        <v>122850931</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3060,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558301</v>
+        <v>558298</v>
       </c>
       <c r="R23" t="n">
-        <v>6415402</v>
+        <v>6415413</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850848</v>
+        <v>122850566</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,10 +3167,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558303</v>
+        <v>558328</v>
       </c>
       <c r="R24" t="n">
-        <v>6415374</v>
+        <v>6415288</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850835</v>
+        <v>122850631</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3282,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558314</v>
+        <v>558328</v>
       </c>
       <c r="R25" t="n">
-        <v>6415377</v>
+        <v>6415300</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,10 +3341,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850740</v>
+        <v>122850580</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,14 +3385,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558324</v>
+        <v>558326</v>
       </c>
       <c r="R26" t="n">
-        <v>6415313</v>
+        <v>6415304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,10 +3452,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851040</v>
+        <v>122851047</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558287</v>
+        <v>558301</v>
       </c>
       <c r="R27" t="n">
-        <v>6415363</v>
+        <v>6415402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851029</v>
+        <v>122850715</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3615,10 +3611,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558287</v>
+        <v>558327</v>
       </c>
       <c r="R28" t="n">
-        <v>6415378</v>
+        <v>6415304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3678,10 +3674,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850658</v>
+        <v>122850835</v>
       </c>
       <c r="B29" t="n">
-        <v>92225</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3690,34 +3686,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3725,10 +3722,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558326</v>
+        <v>558314</v>
       </c>
       <c r="R29" t="n">
-        <v>6415300</v>
+        <v>6415377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,10 +3785,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850991</v>
+        <v>122851065</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558288</v>
+        <v>558266</v>
       </c>
       <c r="R30" t="n">
-        <v>6415391</v>
+        <v>6415358</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,10 +3896,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851054</v>
+        <v>122850918</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3947,10 +3944,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558287</v>
+        <v>558314</v>
       </c>
       <c r="R31" t="n">
-        <v>6415354</v>
+        <v>6415393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850800</v>
+        <v>122850696</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4022,35 +4019,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4058,13 +4059,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558344</v>
+        <v>558333</v>
       </c>
       <c r="R32" t="n">
-        <v>6415332</v>
+        <v>6415302</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4102,7 +4103,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851012</v>
+        <v>122850848</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558276</v>
+        <v>558303</v>
       </c>
       <c r="R33" t="n">
-        <v>6415383</v>
+        <v>6415374</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4235,7 +4235,7 @@
         <v>122850974</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850920</v>
+        <v>122851040</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558291</v>
+        <v>558287</v>
       </c>
       <c r="R35" t="n">
-        <v>6415409</v>
+        <v>6415363</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122851058</v>
+        <v>122850599</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558281</v>
+        <v>558331</v>
       </c>
       <c r="R10" t="n">
-        <v>6415357</v>
+        <v>6415292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122851054</v>
+        <v>122851058</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558287</v>
+        <v>558281</v>
       </c>
       <c r="R11" t="n">
-        <v>6415354</v>
+        <v>6415357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850599</v>
+        <v>122851054</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558331</v>
+        <v>558287</v>
       </c>
       <c r="R12" t="n">
-        <v>6415292</v>
+        <v>6415354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850566</v>
+        <v>122850580</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3163,14 +3163,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558328</v>
+        <v>558326</v>
       </c>
       <c r="R24" t="n">
-        <v>6415288</v>
+        <v>6415304</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850631</v>
+        <v>122850566</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3281,7 +3281,7 @@
         <v>558328</v>
       </c>
       <c r="R25" t="n">
-        <v>6415300</v>
+        <v>6415288</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850580</v>
+        <v>122850631</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3385,14 +3385,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558326</v>
+        <v>558328</v>
       </c>
       <c r="R26" t="n">
-        <v>6415304</v>
+        <v>6415300</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850920</v>
+        <v>122850696</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558291</v>
+        <v>558333</v>
       </c>
       <c r="R2" t="n">
-        <v>6415409</v>
+        <v>6415302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850991</v>
+        <v>122850746</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558288</v>
+        <v>558336</v>
       </c>
       <c r="R3" t="n">
-        <v>6415391</v>
+        <v>6415318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850937</v>
+        <v>122851076</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558285</v>
+        <v>558271</v>
       </c>
       <c r="R4" t="n">
-        <v>6415400</v>
+        <v>6415361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850746</v>
+        <v>122850882</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558336</v>
+        <v>558304</v>
       </c>
       <c r="R5" t="n">
-        <v>6415318</v>
+        <v>6415376</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122851029</v>
+        <v>122850991</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558287</v>
+        <v>558288</v>
       </c>
       <c r="R6" t="n">
-        <v>6415378</v>
+        <v>6415391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850740</v>
+        <v>122851040</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558324</v>
+        <v>558287</v>
       </c>
       <c r="R7" t="n">
-        <v>6415313</v>
+        <v>6415363</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850865</v>
+        <v>122850538</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558306</v>
+        <v>558333</v>
       </c>
       <c r="R8" t="n">
-        <v>6415378</v>
+        <v>6415279</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851076</v>
+        <v>122850800</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558271</v>
+        <v>558344</v>
       </c>
       <c r="R9" t="n">
-        <v>6415361</v>
+        <v>6415332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850599</v>
+        <v>122850931</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558331</v>
+        <v>558298</v>
       </c>
       <c r="R10" t="n">
-        <v>6415292</v>
+        <v>6415413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122851058</v>
+        <v>122850848</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558281</v>
+        <v>558303</v>
       </c>
       <c r="R11" t="n">
-        <v>6415357</v>
+        <v>6415374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122851054</v>
+        <v>122850937</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558287</v>
+        <v>558285</v>
       </c>
       <c r="R12" t="n">
-        <v>6415354</v>
+        <v>6415400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850913</v>
+        <v>122851054</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558297</v>
+        <v>558287</v>
       </c>
       <c r="R13" t="n">
-        <v>6415398</v>
+        <v>6415354</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850658</v>
+        <v>122850835</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,34 +2022,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558326</v>
+        <v>558314</v>
       </c>
       <c r="R14" t="n">
-        <v>6415300</v>
+        <v>6415377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122851099</v>
+        <v>122850918</v>
       </c>
       <c r="B15" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,39 +2133,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2169,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558307</v>
+        <v>558314</v>
       </c>
       <c r="R15" t="n">
-        <v>6415333</v>
+        <v>6415393</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,6 +2213,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2231,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850538</v>
+        <v>122850658</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2243,35 +2244,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558333</v>
+        <v>558326</v>
       </c>
       <c r="R16" t="n">
-        <v>6415279</v>
+        <v>6415300</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851012</v>
+        <v>122850865</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558276</v>
+        <v>558306</v>
       </c>
       <c r="R17" t="n">
-        <v>6415383</v>
+        <v>6415378</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850882</v>
+        <v>122851047</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558304</v>
+        <v>558301</v>
       </c>
       <c r="R18" t="n">
-        <v>6415376</v>
+        <v>6415402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850816</v>
+        <v>122850740</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558317</v>
+        <v>558324</v>
       </c>
       <c r="R19" t="n">
-        <v>6415367</v>
+        <v>6415313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850800</v>
+        <v>122851065</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558344</v>
+        <v>558266</v>
       </c>
       <c r="R20" t="n">
-        <v>6415332</v>
+        <v>6415358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2786,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850901</v>
+        <v>122850785</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558311</v>
+        <v>558330</v>
       </c>
       <c r="R21" t="n">
-        <v>6415391</v>
+        <v>6415337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850785</v>
+        <v>122850566</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558330</v>
+        <v>558328</v>
       </c>
       <c r="R22" t="n">
-        <v>6415337</v>
+        <v>6415288</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850931</v>
+        <v>122850901</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558298</v>
+        <v>558311</v>
       </c>
       <c r="R23" t="n">
-        <v>6415413</v>
+        <v>6415391</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850580</v>
+        <v>122850913</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3163,14 +3163,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558326</v>
+        <v>558297</v>
       </c>
       <c r="R24" t="n">
-        <v>6415304</v>
+        <v>6415398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850566</v>
+        <v>122850974</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558328</v>
+        <v>558285</v>
       </c>
       <c r="R25" t="n">
-        <v>6415288</v>
+        <v>6415397</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850631</v>
+        <v>122850715</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558328</v>
+        <v>558327</v>
       </c>
       <c r="R26" t="n">
-        <v>6415300</v>
+        <v>6415304</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851047</v>
+        <v>122850816</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3500,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558301</v>
+        <v>558317</v>
       </c>
       <c r="R27" t="n">
-        <v>6415402</v>
+        <v>6415367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850715</v>
+        <v>122850580</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3607,11 +3607,11 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558327</v>
+        <v>558326</v>
       </c>
       <c r="R28" t="n">
         <v>6415304</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850835</v>
+        <v>122850599</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558314</v>
+        <v>558331</v>
       </c>
       <c r="R29" t="n">
-        <v>6415377</v>
+        <v>6415292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851065</v>
+        <v>122850920</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558266</v>
+        <v>558291</v>
       </c>
       <c r="R30" t="n">
-        <v>6415358</v>
+        <v>6415409</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850918</v>
+        <v>122850631</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558314</v>
+        <v>558328</v>
       </c>
       <c r="R31" t="n">
-        <v>6415393</v>
+        <v>6415300</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850696</v>
+        <v>122851029</v>
       </c>
       <c r="B32" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4019,39 +4019,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4059,13 +4055,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R32" t="n">
-        <v>6415302</v>
+        <v>6415378</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4103,6 +4099,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4121,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850848</v>
+        <v>122851099</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4133,35 +4130,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4169,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558303</v>
+        <v>558307</v>
       </c>
       <c r="R33" t="n">
-        <v>6415374</v>
+        <v>6415333</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,7 +4214,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850974</v>
+        <v>122851058</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558285</v>
+        <v>558281</v>
       </c>
       <c r="R34" t="n">
-        <v>6415397</v>
+        <v>6415357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851040</v>
+        <v>122851012</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558287</v>
+        <v>558276</v>
       </c>
       <c r="R35" t="n">
-        <v>6415363</v>
+        <v>6415383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850696</v>
+        <v>122850746</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558333</v>
+        <v>558336</v>
       </c>
       <c r="R2" t="n">
-        <v>6415302</v>
+        <v>6415318</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850746</v>
+        <v>122850696</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558336</v>
+        <v>558333</v>
       </c>
       <c r="R3" t="n">
-        <v>6415318</v>
+        <v>6415302</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850865</v>
+        <v>122851047</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558306</v>
+        <v>558301</v>
       </c>
       <c r="R17" t="n">
-        <v>6415378</v>
+        <v>6415402</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851047</v>
+        <v>122850865</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558301</v>
+        <v>558306</v>
       </c>
       <c r="R18" t="n">
-        <v>6415402</v>
+        <v>6415378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850974</v>
+        <v>122850715</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558285</v>
+        <v>558327</v>
       </c>
       <c r="R25" t="n">
-        <v>6415397</v>
+        <v>6415304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850715</v>
+        <v>122850974</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558327</v>
+        <v>558285</v>
       </c>
       <c r="R26" t="n">
-        <v>6415304</v>
+        <v>6415397</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850746</v>
+        <v>122850696</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558336</v>
+        <v>558333</v>
       </c>
       <c r="R2" t="n">
-        <v>6415318</v>
+        <v>6415302</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850696</v>
+        <v>122850746</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558333</v>
+        <v>558336</v>
       </c>
       <c r="R3" t="n">
-        <v>6415302</v>
+        <v>6415318</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850696</v>
+        <v>122851058</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558333</v>
+        <v>558281</v>
       </c>
       <c r="R2" t="n">
-        <v>6415302</v>
+        <v>6415357</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850746</v>
+        <v>122851012</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558336</v>
+        <v>558276</v>
       </c>
       <c r="R3" t="n">
-        <v>6415318</v>
+        <v>6415383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122851076</v>
+        <v>122850901</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558271</v>
+        <v>558311</v>
       </c>
       <c r="R4" t="n">
-        <v>6415361</v>
+        <v>6415391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850882</v>
+        <v>122850931</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558304</v>
+        <v>558298</v>
       </c>
       <c r="R5" t="n">
-        <v>6415376</v>
+        <v>6415413</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850991</v>
+        <v>122850566</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558288</v>
+        <v>558328</v>
       </c>
       <c r="R6" t="n">
-        <v>6415391</v>
+        <v>6415288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122851040</v>
+        <v>122850835</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558287</v>
+        <v>558314</v>
       </c>
       <c r="R7" t="n">
-        <v>6415363</v>
+        <v>6415377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850538</v>
+        <v>122851040</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1392,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R8" t="n">
-        <v>6415279</v>
+        <v>6415363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850800</v>
+        <v>122850746</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1503,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558344</v>
+        <v>558336</v>
       </c>
       <c r="R9" t="n">
-        <v>6415332</v>
+        <v>6415318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850931</v>
+        <v>122850740</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1614,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558298</v>
+        <v>558324</v>
       </c>
       <c r="R10" t="n">
-        <v>6415413</v>
+        <v>6415313</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850848</v>
+        <v>122850918</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1725,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558303</v>
+        <v>558314</v>
       </c>
       <c r="R11" t="n">
-        <v>6415374</v>
+        <v>6415393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850937</v>
+        <v>122850538</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1836,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558285</v>
+        <v>558333</v>
       </c>
       <c r="R12" t="n">
-        <v>6415400</v>
+        <v>6415279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122851054</v>
+        <v>122851065</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1947,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558287</v>
+        <v>558266</v>
       </c>
       <c r="R13" t="n">
-        <v>6415354</v>
+        <v>6415358</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850835</v>
+        <v>122850816</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2058,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558314</v>
+        <v>558317</v>
       </c>
       <c r="R14" t="n">
-        <v>6415377</v>
+        <v>6415367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850918</v>
+        <v>122850631</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2169,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558314</v>
+        <v>558328</v>
       </c>
       <c r="R15" t="n">
-        <v>6415393</v>
+        <v>6415300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850658</v>
+        <v>122851099</v>
       </c>
       <c r="B16" t="n">
-        <v>92233</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,30 +2245,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2279,13 +2281,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558326</v>
+        <v>558307</v>
       </c>
       <c r="R16" t="n">
-        <v>6415300</v>
+        <v>6415333</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,7 +2325,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2342,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851047</v>
+        <v>122850580</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2386,14 +2387,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558301</v>
+        <v>558326</v>
       </c>
       <c r="R17" t="n">
-        <v>6415402</v>
+        <v>6415304</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850865</v>
+        <v>122850848</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2501,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558306</v>
+        <v>558303</v>
       </c>
       <c r="R18" t="n">
-        <v>6415378</v>
+        <v>6415374</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850740</v>
+        <v>122850715</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2612,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558324</v>
+        <v>558327</v>
       </c>
       <c r="R19" t="n">
-        <v>6415313</v>
+        <v>6415304</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851065</v>
+        <v>122851054</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2723,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558266</v>
+        <v>558287</v>
       </c>
       <c r="R20" t="n">
-        <v>6415358</v>
+        <v>6415354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850785</v>
+        <v>122850800</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2834,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558330</v>
+        <v>558344</v>
       </c>
       <c r="R21" t="n">
-        <v>6415337</v>
+        <v>6415332</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850566</v>
+        <v>122850882</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -2945,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558328</v>
+        <v>558304</v>
       </c>
       <c r="R22" t="n">
-        <v>6415288</v>
+        <v>6415376</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850901</v>
+        <v>122850974</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558311</v>
+        <v>558285</v>
       </c>
       <c r="R23" t="n">
-        <v>6415391</v>
+        <v>6415397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3119,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850913</v>
+        <v>122851047</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3167,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558297</v>
+        <v>558301</v>
       </c>
       <c r="R24" t="n">
-        <v>6415398</v>
+        <v>6415402</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850715</v>
+        <v>122850937</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3278,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558327</v>
+        <v>558285</v>
       </c>
       <c r="R25" t="n">
-        <v>6415304</v>
+        <v>6415400</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850974</v>
+        <v>122850913</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3389,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558285</v>
+        <v>558297</v>
       </c>
       <c r="R26" t="n">
-        <v>6415397</v>
+        <v>6415398</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850816</v>
+        <v>122850696</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3464,35 +3465,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3500,13 +3505,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558317</v>
+        <v>558333</v>
       </c>
       <c r="R27" t="n">
-        <v>6415367</v>
+        <v>6415302</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,7 +3549,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3563,7 +3567,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850580</v>
+        <v>122850599</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3607,14 +3611,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558326</v>
+        <v>558331</v>
       </c>
       <c r="R28" t="n">
-        <v>6415304</v>
+        <v>6415292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,7 +3678,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850599</v>
+        <v>122850785</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3722,10 +3726,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558331</v>
+        <v>558330</v>
       </c>
       <c r="R29" t="n">
-        <v>6415292</v>
+        <v>6415337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,7 +3789,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850920</v>
+        <v>122851076</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3833,10 +3837,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558291</v>
+        <v>558271</v>
       </c>
       <c r="R30" t="n">
-        <v>6415409</v>
+        <v>6415361</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3896,10 +3900,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850631</v>
+        <v>122850658</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3908,35 +3912,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3944,7 +3947,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558328</v>
+        <v>558326</v>
       </c>
       <c r="R31" t="n">
         <v>6415300</v>
@@ -4007,7 +4010,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851029</v>
+        <v>122850991</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4055,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558287</v>
+        <v>558288</v>
       </c>
       <c r="R32" t="n">
-        <v>6415378</v>
+        <v>6415391</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4118,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851099</v>
+        <v>122850920</v>
       </c>
       <c r="B33" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4130,39 +4133,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4170,13 +4169,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558307</v>
+        <v>558291</v>
       </c>
       <c r="R33" t="n">
-        <v>6415333</v>
+        <v>6415409</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4214,6 +4213,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851058</v>
+        <v>122850865</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558281</v>
+        <v>558306</v>
       </c>
       <c r="R34" t="n">
-        <v>6415357</v>
+        <v>6415378</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851012</v>
+        <v>122851029</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558276</v>
+        <v>558287</v>
       </c>
       <c r="R35" t="n">
-        <v>6415383</v>
+        <v>6415378</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122851058</v>
+        <v>122850740</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558281</v>
+        <v>558324</v>
       </c>
       <c r="R2" t="n">
-        <v>6415357</v>
+        <v>6415313</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122851012</v>
+        <v>122850715</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558276</v>
+        <v>558327</v>
       </c>
       <c r="R3" t="n">
-        <v>6415383</v>
+        <v>6415304</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850901</v>
+        <v>122850931</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558311</v>
+        <v>558298</v>
       </c>
       <c r="R4" t="n">
-        <v>6415391</v>
+        <v>6415413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850931</v>
+        <v>122851047</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558298</v>
+        <v>558301</v>
       </c>
       <c r="R5" t="n">
-        <v>6415413</v>
+        <v>6415402</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850566</v>
+        <v>122850580</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558328</v>
+        <v>558326</v>
       </c>
       <c r="R6" t="n">
-        <v>6415288</v>
+        <v>6415304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850835</v>
+        <v>122850882</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558314</v>
+        <v>558304</v>
       </c>
       <c r="R7" t="n">
-        <v>6415377</v>
+        <v>6415376</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122851040</v>
+        <v>122850901</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558287</v>
+        <v>558311</v>
       </c>
       <c r="R8" t="n">
-        <v>6415363</v>
+        <v>6415391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122850746</v>
+        <v>122851040</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558336</v>
+        <v>558287</v>
       </c>
       <c r="R9" t="n">
-        <v>6415318</v>
+        <v>6415363</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850740</v>
+        <v>122850746</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558324</v>
+        <v>558336</v>
       </c>
       <c r="R10" t="n">
-        <v>6415313</v>
+        <v>6415318</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850918</v>
+        <v>122850785</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558314</v>
+        <v>558330</v>
       </c>
       <c r="R11" t="n">
-        <v>6415393</v>
+        <v>6415337</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850538</v>
+        <v>122850848</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558333</v>
+        <v>558303</v>
       </c>
       <c r="R12" t="n">
-        <v>6415279</v>
+        <v>6415374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122851065</v>
+        <v>122850865</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558266</v>
+        <v>558306</v>
       </c>
       <c r="R13" t="n">
-        <v>6415358</v>
+        <v>6415378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850816</v>
+        <v>122850599</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558317</v>
+        <v>558331</v>
       </c>
       <c r="R14" t="n">
-        <v>6415367</v>
+        <v>6415292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850631</v>
+        <v>122851099</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,35 +2130,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2166,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558328</v>
+        <v>558307</v>
       </c>
       <c r="R15" t="n">
-        <v>6415300</v>
+        <v>6415333</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,7 +2214,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2229,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851099</v>
+        <v>122850631</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,39 +2244,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2281,13 +2280,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558307</v>
+        <v>558328</v>
       </c>
       <c r="R16" t="n">
-        <v>6415333</v>
+        <v>6415300</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2325,6 +2324,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850580</v>
+        <v>122850920</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2387,14 +2387,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558326</v>
+        <v>558291</v>
       </c>
       <c r="R17" t="n">
-        <v>6415304</v>
+        <v>6415409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850848</v>
+        <v>122850913</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558303</v>
+        <v>558297</v>
       </c>
       <c r="R18" t="n">
-        <v>6415374</v>
+        <v>6415398</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850715</v>
+        <v>122850800</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558327</v>
+        <v>558344</v>
       </c>
       <c r="R19" t="n">
-        <v>6415304</v>
+        <v>6415332</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851054</v>
+        <v>122850816</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558287</v>
+        <v>558317</v>
       </c>
       <c r="R20" t="n">
-        <v>6415354</v>
+        <v>6415367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850800</v>
+        <v>122850991</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558344</v>
+        <v>558288</v>
       </c>
       <c r="R21" t="n">
-        <v>6415332</v>
+        <v>6415391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850882</v>
+        <v>122851076</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558304</v>
+        <v>558271</v>
       </c>
       <c r="R22" t="n">
-        <v>6415376</v>
+        <v>6415361</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850974</v>
+        <v>122850538</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558285</v>
+        <v>558333</v>
       </c>
       <c r="R23" t="n">
-        <v>6415397</v>
+        <v>6415279</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851047</v>
+        <v>122850974</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558301</v>
+        <v>558285</v>
       </c>
       <c r="R24" t="n">
-        <v>6415402</v>
+        <v>6415397</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850937</v>
+        <v>122851065</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558285</v>
+        <v>558266</v>
       </c>
       <c r="R25" t="n">
-        <v>6415400</v>
+        <v>6415358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850913</v>
+        <v>122851029</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558297</v>
+        <v>558287</v>
       </c>
       <c r="R26" t="n">
-        <v>6415398</v>
+        <v>6415378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850696</v>
+        <v>122851054</v>
       </c>
       <c r="B27" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,39 +3465,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3505,13 +3501,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R27" t="n">
-        <v>6415302</v>
+        <v>6415354</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3549,6 +3545,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3567,7 +3564,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850599</v>
+        <v>122851058</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -3615,10 +3612,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558331</v>
+        <v>558281</v>
       </c>
       <c r="R28" t="n">
-        <v>6415292</v>
+        <v>6415357</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3678,7 +3675,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850785</v>
+        <v>122850918</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3726,10 +3723,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558330</v>
+        <v>558314</v>
       </c>
       <c r="R29" t="n">
-        <v>6415337</v>
+        <v>6415393</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3786,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851076</v>
+        <v>122851012</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -3837,10 +3834,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558271</v>
+        <v>558276</v>
       </c>
       <c r="R30" t="n">
-        <v>6415361</v>
+        <v>6415383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3900,10 +3897,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850658</v>
+        <v>122850937</v>
       </c>
       <c r="B31" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3912,34 +3909,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3947,10 +3945,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558326</v>
+        <v>558285</v>
       </c>
       <c r="R31" t="n">
-        <v>6415300</v>
+        <v>6415400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,10 +4008,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850991</v>
+        <v>122850658</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4022,35 +4020,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4058,10 +4055,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558288</v>
+        <v>558326</v>
       </c>
       <c r="R32" t="n">
-        <v>6415391</v>
+        <v>6415300</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850920</v>
+        <v>122850696</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4133,35 +4130,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4169,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558291</v>
+        <v>558333</v>
       </c>
       <c r="R33" t="n">
-        <v>6415409</v>
+        <v>6415302</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4213,7 +4214,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850865</v>
+        <v>122850566</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558306</v>
+        <v>558328</v>
       </c>
       <c r="R34" t="n">
-        <v>6415378</v>
+        <v>6415288</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851029</v>
+        <v>122850835</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558287</v>
+        <v>558314</v>
       </c>
       <c r="R35" t="n">
-        <v>6415378</v>
+        <v>6415377</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850740</v>
+        <v>122850800</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558324</v>
+        <v>558344</v>
       </c>
       <c r="R2" t="n">
-        <v>6415313</v>
+        <v>6415332</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850715</v>
+        <v>122850918</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558327</v>
+        <v>558314</v>
       </c>
       <c r="R3" t="n">
-        <v>6415304</v>
+        <v>6415393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850931</v>
+        <v>122850913</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558298</v>
+        <v>558297</v>
       </c>
       <c r="R4" t="n">
-        <v>6415413</v>
+        <v>6415398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122851047</v>
+        <v>122850740</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558301</v>
+        <v>558324</v>
       </c>
       <c r="R5" t="n">
-        <v>6415402</v>
+        <v>6415313</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850580</v>
+        <v>122850835</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558326</v>
+        <v>558314</v>
       </c>
       <c r="R6" t="n">
-        <v>6415304</v>
+        <v>6415377</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850882</v>
+        <v>122850746</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558304</v>
+        <v>558336</v>
       </c>
       <c r="R7" t="n">
-        <v>6415376</v>
+        <v>6415318</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850901</v>
+        <v>122851029</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558311</v>
+        <v>558287</v>
       </c>
       <c r="R8" t="n">
-        <v>6415391</v>
+        <v>6415378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851040</v>
+        <v>122851047</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558287</v>
+        <v>558301</v>
       </c>
       <c r="R9" t="n">
-        <v>6415363</v>
+        <v>6415402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850746</v>
+        <v>122850816</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558336</v>
+        <v>558317</v>
       </c>
       <c r="R10" t="n">
-        <v>6415318</v>
+        <v>6415367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850785</v>
+        <v>122850920</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558330</v>
+        <v>558291</v>
       </c>
       <c r="R11" t="n">
-        <v>6415337</v>
+        <v>6415409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850848</v>
+        <v>122851065</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558303</v>
+        <v>558266</v>
       </c>
       <c r="R12" t="n">
-        <v>6415374</v>
+        <v>6415358</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850865</v>
+        <v>122850848</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558306</v>
+        <v>558303</v>
       </c>
       <c r="R13" t="n">
-        <v>6415378</v>
+        <v>6415374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850599</v>
+        <v>122851040</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558331</v>
+        <v>558287</v>
       </c>
       <c r="R14" t="n">
-        <v>6415292</v>
+        <v>6415363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122851099</v>
+        <v>122850631</v>
       </c>
       <c r="B15" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,39 +2130,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2170,13 +2166,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558307</v>
+        <v>558328</v>
       </c>
       <c r="R15" t="n">
-        <v>6415333</v>
+        <v>6415300</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,6 +2210,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850631</v>
+        <v>122850658</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,35 +2241,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2280,7 +2276,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558328</v>
+        <v>558326</v>
       </c>
       <c r="R16" t="n">
         <v>6415300</v>
@@ -2343,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850920</v>
+        <v>122851058</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558291</v>
+        <v>558281</v>
       </c>
       <c r="R17" t="n">
-        <v>6415409</v>
+        <v>6415357</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850913</v>
+        <v>122850566</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558297</v>
+        <v>558328</v>
       </c>
       <c r="R18" t="n">
-        <v>6415398</v>
+        <v>6415288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850800</v>
+        <v>122850865</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2613,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558344</v>
+        <v>558306</v>
       </c>
       <c r="R19" t="n">
-        <v>6415332</v>
+        <v>6415378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850816</v>
+        <v>122850974</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558317</v>
+        <v>558285</v>
       </c>
       <c r="R20" t="n">
-        <v>6415367</v>
+        <v>6415397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850991</v>
+        <v>122850785</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558288</v>
+        <v>558330</v>
       </c>
       <c r="R21" t="n">
-        <v>6415391</v>
+        <v>6415337</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851076</v>
+        <v>122850580</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,14 +2938,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558271</v>
+        <v>558326</v>
       </c>
       <c r="R22" t="n">
-        <v>6415361</v>
+        <v>6415304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850538</v>
+        <v>122850599</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,10 +3053,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558333</v>
+        <v>558331</v>
       </c>
       <c r="R23" t="n">
-        <v>6415279</v>
+        <v>6415292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3116,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850974</v>
+        <v>122850991</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558285</v>
+        <v>558288</v>
       </c>
       <c r="R24" t="n">
-        <v>6415397</v>
+        <v>6415391</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851065</v>
+        <v>122851054</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3279,10 +3275,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558266</v>
+        <v>558287</v>
       </c>
       <c r="R25" t="n">
-        <v>6415358</v>
+        <v>6415354</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3342,10 +3338,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851029</v>
+        <v>122850882</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3390,10 +3386,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558287</v>
+        <v>558304</v>
       </c>
       <c r="R26" t="n">
-        <v>6415378</v>
+        <v>6415376</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,10 +3449,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851054</v>
+        <v>122850538</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,10 +3497,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558287</v>
+        <v>558333</v>
       </c>
       <c r="R27" t="n">
-        <v>6415354</v>
+        <v>6415279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,10 +3560,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851058</v>
+        <v>122851012</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558281</v>
+        <v>558276</v>
       </c>
       <c r="R28" t="n">
-        <v>6415357</v>
+        <v>6415383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,10 +3671,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850918</v>
+        <v>122850901</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3723,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558314</v>
+        <v>558311</v>
       </c>
       <c r="R29" t="n">
-        <v>6415393</v>
+        <v>6415391</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,10 +3782,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851012</v>
+        <v>122850931</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3834,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558276</v>
+        <v>558298</v>
       </c>
       <c r="R30" t="n">
-        <v>6415383</v>
+        <v>6415413</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3900,7 +3896,7 @@
         <v>122850937</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4008,10 +4004,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850658</v>
+        <v>122850696</v>
       </c>
       <c r="B32" t="n">
-        <v>92233</v>
+        <v>57634</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4020,34 +4016,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4055,13 +4056,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558326</v>
+        <v>558333</v>
       </c>
       <c r="R32" t="n">
-        <v>6415300</v>
+        <v>6415302</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4099,7 +4100,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4118,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850696</v>
+        <v>122851099</v>
       </c>
       <c r="B33" t="n">
-        <v>57631</v>
+        <v>57851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4130,25 +4130,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4160,7 +4160,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558333</v>
+        <v>558307</v>
       </c>
       <c r="R33" t="n">
-        <v>6415302</v>
+        <v>6415333</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850566</v>
+        <v>122851076</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558328</v>
+        <v>558271</v>
       </c>
       <c r="R34" t="n">
-        <v>6415288</v>
+        <v>6415361</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850835</v>
+        <v>122850715</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558314</v>
+        <v>558327</v>
       </c>
       <c r="R35" t="n">
-        <v>6415377</v>
+        <v>6415304</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122850800</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850918</v>
+        <v>122851099</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558314</v>
+        <v>558307</v>
       </c>
       <c r="R3" t="n">
-        <v>6415393</v>
+        <v>6415333</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850913</v>
+        <v>122851047</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558297</v>
+        <v>558301</v>
       </c>
       <c r="R4" t="n">
-        <v>6415398</v>
+        <v>6415402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850740</v>
+        <v>122851040</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558324</v>
+        <v>558287</v>
       </c>
       <c r="R5" t="n">
-        <v>6415313</v>
+        <v>6415363</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850835</v>
+        <v>122850848</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558314</v>
+        <v>558303</v>
       </c>
       <c r="R6" t="n">
-        <v>6415377</v>
+        <v>6415374</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850746</v>
+        <v>122850931</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558336</v>
+        <v>558298</v>
       </c>
       <c r="R7" t="n">
-        <v>6415318</v>
+        <v>6415413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122851029</v>
+        <v>122850865</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,7 +1392,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558287</v>
+        <v>558306</v>
       </c>
       <c r="R8" t="n">
         <v>6415378</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851047</v>
+        <v>122851076</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558301</v>
+        <v>558271</v>
       </c>
       <c r="R9" t="n">
-        <v>6415402</v>
+        <v>6415361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850816</v>
+        <v>122850599</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558317</v>
+        <v>558331</v>
       </c>
       <c r="R10" t="n">
-        <v>6415367</v>
+        <v>6415292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850920</v>
+        <v>122850785</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558291</v>
+        <v>558330</v>
       </c>
       <c r="R11" t="n">
-        <v>6415409</v>
+        <v>6415337</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122851065</v>
+        <v>122850918</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558266</v>
+        <v>558314</v>
       </c>
       <c r="R12" t="n">
-        <v>6415358</v>
+        <v>6415393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850848</v>
+        <v>122850901</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558303</v>
+        <v>558311</v>
       </c>
       <c r="R13" t="n">
-        <v>6415374</v>
+        <v>6415391</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122851040</v>
+        <v>122850974</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558287</v>
+        <v>558285</v>
       </c>
       <c r="R14" t="n">
-        <v>6415363</v>
+        <v>6415397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850631</v>
+        <v>122850913</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558328</v>
+        <v>558297</v>
       </c>
       <c r="R15" t="n">
-        <v>6415300</v>
+        <v>6415398</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850658</v>
+        <v>122850835</v>
       </c>
       <c r="B16" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,34 +2244,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2276,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558326</v>
+        <v>558314</v>
       </c>
       <c r="R16" t="n">
-        <v>6415300</v>
+        <v>6415377</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851058</v>
+        <v>122851012</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558281</v>
+        <v>558276</v>
       </c>
       <c r="R17" t="n">
-        <v>6415357</v>
+        <v>6415383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2450,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850566</v>
+        <v>122850991</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558328</v>
+        <v>558288</v>
       </c>
       <c r="R18" t="n">
-        <v>6415288</v>
+        <v>6415391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850865</v>
+        <v>122850658</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,35 +2577,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2609,10 +2612,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558306</v>
+        <v>558326</v>
       </c>
       <c r="R19" t="n">
-        <v>6415378</v>
+        <v>6415300</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2672,10 +2675,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850974</v>
+        <v>122850882</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,10 +2723,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558285</v>
+        <v>558304</v>
       </c>
       <c r="R20" t="n">
-        <v>6415397</v>
+        <v>6415376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,10 +2786,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850785</v>
+        <v>122850746</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,10 +2834,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558330</v>
+        <v>558336</v>
       </c>
       <c r="R21" t="n">
-        <v>6415337</v>
+        <v>6415318</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2894,10 +2897,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850580</v>
+        <v>122850816</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2938,14 +2941,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558326</v>
+        <v>558317</v>
       </c>
       <c r="R22" t="n">
-        <v>6415304</v>
+        <v>6415367</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850599</v>
+        <v>122850566</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,10 +3056,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558331</v>
+        <v>558328</v>
       </c>
       <c r="R23" t="n">
-        <v>6415292</v>
+        <v>6415288</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3116,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850991</v>
+        <v>122850580</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,14 +3163,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558288</v>
+        <v>558326</v>
       </c>
       <c r="R24" t="n">
-        <v>6415391</v>
+        <v>6415304</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851054</v>
+        <v>122850715</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3275,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558287</v>
+        <v>558327</v>
       </c>
       <c r="R25" t="n">
-        <v>6415354</v>
+        <v>6415304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,10 +3341,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850882</v>
+        <v>122850740</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,10 +3389,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558304</v>
+        <v>558324</v>
       </c>
       <c r="R26" t="n">
-        <v>6415376</v>
+        <v>6415313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3449,10 +3452,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850538</v>
+        <v>122850631</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,10 +3500,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558333</v>
+        <v>558328</v>
       </c>
       <c r="R27" t="n">
-        <v>6415279</v>
+        <v>6415300</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851012</v>
+        <v>122850696</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3572,35 +3575,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3608,13 +3615,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558276</v>
+        <v>558333</v>
       </c>
       <c r="R28" t="n">
-        <v>6415383</v>
+        <v>6415302</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3652,7 +3659,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3671,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122850901</v>
+        <v>122851029</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558311</v>
+        <v>558287</v>
       </c>
       <c r="R29" t="n">
-        <v>6415391</v>
+        <v>6415378</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3782,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850931</v>
+        <v>122850920</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558298</v>
+        <v>558291</v>
       </c>
       <c r="R30" t="n">
-        <v>6415413</v>
+        <v>6415409</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3893,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850937</v>
+        <v>122850538</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3941,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558285</v>
+        <v>558333</v>
       </c>
       <c r="R31" t="n">
-        <v>6415400</v>
+        <v>6415279</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4004,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850696</v>
+        <v>122851065</v>
       </c>
       <c r="B32" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4016,39 +4022,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4056,13 +4058,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558333</v>
+        <v>558266</v>
       </c>
       <c r="R32" t="n">
-        <v>6415302</v>
+        <v>6415358</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,6 +4102,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4118,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851099</v>
+        <v>122851058</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4130,39 +4133,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4170,13 +4169,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558307</v>
+        <v>558281</v>
       </c>
       <c r="R33" t="n">
-        <v>6415333</v>
+        <v>6415357</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4214,6 +4213,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851076</v>
+        <v>122850937</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558271</v>
+        <v>558285</v>
       </c>
       <c r="R34" t="n">
-        <v>6415361</v>
+        <v>6415400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850715</v>
+        <v>122851054</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558327</v>
+        <v>558287</v>
       </c>
       <c r="R35" t="n">
-        <v>6415304</v>
+        <v>6415354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850800</v>
+        <v>122850658</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558344</v>
+        <v>558326</v>
       </c>
       <c r="R2" t="n">
-        <v>6415332</v>
+        <v>6415300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122851099</v>
+        <v>122850631</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558307</v>
+        <v>558328</v>
       </c>
       <c r="R3" t="n">
-        <v>6415333</v>
+        <v>6415300</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +877,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122851047</v>
+        <v>122850580</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,14 +940,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558301</v>
+        <v>558326</v>
       </c>
       <c r="R4" t="n">
-        <v>6415402</v>
+        <v>6415304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122851040</v>
+        <v>122850937</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558287</v>
+        <v>558285</v>
       </c>
       <c r="R5" t="n">
-        <v>6415363</v>
+        <v>6415400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850848</v>
+        <v>122850599</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558303</v>
+        <v>558331</v>
       </c>
       <c r="R6" t="n">
-        <v>6415374</v>
+        <v>6415292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850931</v>
+        <v>122850835</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558298</v>
+        <v>558314</v>
       </c>
       <c r="R7" t="n">
-        <v>6415413</v>
+        <v>6415377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850865</v>
+        <v>122850566</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558306</v>
+        <v>558328</v>
       </c>
       <c r="R8" t="n">
-        <v>6415378</v>
+        <v>6415288</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851076</v>
+        <v>122851047</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558271</v>
+        <v>558301</v>
       </c>
       <c r="R9" t="n">
-        <v>6415361</v>
+        <v>6415402</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122850599</v>
+        <v>122851065</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1610,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558331</v>
+        <v>558266</v>
       </c>
       <c r="R10" t="n">
-        <v>6415292</v>
+        <v>6415358</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122850785</v>
+        <v>122851012</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558330</v>
+        <v>558276</v>
       </c>
       <c r="R11" t="n">
-        <v>6415337</v>
+        <v>6415383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1784,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850918</v>
+        <v>122850740</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558314</v>
+        <v>558324</v>
       </c>
       <c r="R12" t="n">
-        <v>6415393</v>
+        <v>6415313</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122850901</v>
+        <v>122851040</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558311</v>
+        <v>558287</v>
       </c>
       <c r="R13" t="n">
-        <v>6415391</v>
+        <v>6415363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122850974</v>
+        <v>122851058</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558285</v>
+        <v>558281</v>
       </c>
       <c r="R14" t="n">
-        <v>6415397</v>
+        <v>6415357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850913</v>
+        <v>122850538</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558297</v>
+        <v>558333</v>
       </c>
       <c r="R15" t="n">
-        <v>6415398</v>
+        <v>6415279</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122850835</v>
+        <v>122851076</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2276,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558314</v>
+        <v>558271</v>
       </c>
       <c r="R16" t="n">
-        <v>6415377</v>
+        <v>6415361</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2339,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122851012</v>
+        <v>122850931</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,10 +2387,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558276</v>
+        <v>558298</v>
       </c>
       <c r="R17" t="n">
-        <v>6415383</v>
+        <v>6415413</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2450,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122850991</v>
+        <v>122850746</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558288</v>
+        <v>558336</v>
       </c>
       <c r="R18" t="n">
-        <v>6415391</v>
+        <v>6415318</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850658</v>
+        <v>122850816</v>
       </c>
       <c r="B19" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2577,34 +2573,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2612,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558326</v>
+        <v>558317</v>
       </c>
       <c r="R19" t="n">
-        <v>6415300</v>
+        <v>6415367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2675,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850882</v>
+        <v>122850920</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,10 +2720,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558304</v>
+        <v>558291</v>
       </c>
       <c r="R20" t="n">
-        <v>6415376</v>
+        <v>6415409</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2786,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850746</v>
+        <v>122850865</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558336</v>
+        <v>558306</v>
       </c>
       <c r="R21" t="n">
-        <v>6415318</v>
+        <v>6415378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2897,10 +2894,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850816</v>
+        <v>122850991</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2945,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558317</v>
+        <v>558288</v>
       </c>
       <c r="R22" t="n">
-        <v>6415367</v>
+        <v>6415391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3008,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850566</v>
+        <v>122850696</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>57634</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,35 +3017,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3056,13 +3057,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558328</v>
+        <v>558333</v>
       </c>
       <c r="R23" t="n">
-        <v>6415288</v>
+        <v>6415302</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3100,7 +3101,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122850580</v>
+        <v>122851054</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3163,14 +3163,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558326</v>
+        <v>558287</v>
       </c>
       <c r="R24" t="n">
-        <v>6415304</v>
+        <v>6415354</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3233,7 @@
         <v>122850715</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850740</v>
+        <v>122851099</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3353,35 +3353,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3389,13 +3393,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558324</v>
+        <v>558307</v>
       </c>
       <c r="R26" t="n">
-        <v>6415313</v>
+        <v>6415333</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3433,7 +3437,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3452,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850631</v>
+        <v>122850918</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3500,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558328</v>
+        <v>558314</v>
       </c>
       <c r="R27" t="n">
-        <v>6415300</v>
+        <v>6415393</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850696</v>
+        <v>122850800</v>
       </c>
       <c r="B28" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3575,39 +3578,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3615,13 +3614,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558333</v>
+        <v>558344</v>
       </c>
       <c r="R28" t="n">
-        <v>6415302</v>
+        <v>6415332</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3659,6 +3658,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>122851029</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850920</v>
+        <v>122850913</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558291</v>
+        <v>558297</v>
       </c>
       <c r="R30" t="n">
-        <v>6415409</v>
+        <v>6415398</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850538</v>
+        <v>122850785</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558333</v>
+        <v>558330</v>
       </c>
       <c r="R31" t="n">
-        <v>6415279</v>
+        <v>6415337</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851065</v>
+        <v>122850848</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558266</v>
+        <v>558303</v>
       </c>
       <c r="R32" t="n">
-        <v>6415358</v>
+        <v>6415374</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851058</v>
+        <v>122850901</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558281</v>
+        <v>558311</v>
       </c>
       <c r="R33" t="n">
-        <v>6415357</v>
+        <v>6415391</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850937</v>
+        <v>122850974</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>558285</v>
       </c>
       <c r="R34" t="n">
-        <v>6415400</v>
+        <v>6415397</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851054</v>
+        <v>122850882</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558287</v>
+        <v>558304</v>
       </c>
       <c r="R35" t="n">
-        <v>6415354</v>
+        <v>6415376</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 6782-2025 artfynd.xlsx
+++ b/artfynd/A 6782-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122850658</v>
+        <v>122850631</v>
       </c>
       <c r="B2" t="n">
-        <v>92244</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,7 +723,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558326</v>
+        <v>558328</v>
       </c>
       <c r="R2" t="n">
         <v>6415300</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122850631</v>
+        <v>122850800</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558328</v>
+        <v>558344</v>
       </c>
       <c r="R3" t="n">
-        <v>6415300</v>
+        <v>6415332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122850580</v>
+        <v>122850538</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 6782, Kila, KInda, Ög</t>
+          <t>A 6782, Kila, Kinda, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558326</v>
+        <v>558333</v>
       </c>
       <c r="R4" t="n">
-        <v>6415304</v>
+        <v>6415279</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122850937</v>
+        <v>122850991</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558285</v>
+        <v>558288</v>
       </c>
       <c r="R5" t="n">
-        <v>6415400</v>
+        <v>6415391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122850599</v>
+        <v>122850580</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,14 +1163,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 6782, Kila, Kinda, Ög</t>
+          <t>A 6782, Kila, KInda, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558331</v>
+        <v>558326</v>
       </c>
       <c r="R6" t="n">
-        <v>6415292</v>
+        <v>6415304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122850835</v>
+        <v>122850715</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558314</v>
+        <v>558327</v>
       </c>
       <c r="R7" t="n">
-        <v>6415377</v>
+        <v>6415304</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122850566</v>
+        <v>122850920</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558328</v>
+        <v>558291</v>
       </c>
       <c r="R8" t="n">
-        <v>6415288</v>
+        <v>6415409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122851047</v>
+        <v>122850865</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558301</v>
+        <v>558306</v>
       </c>
       <c r="R9" t="n">
-        <v>6415402</v>
+        <v>6415378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122851065</v>
+        <v>122850882</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558266</v>
+        <v>558304</v>
       </c>
       <c r="R10" t="n">
-        <v>6415358</v>
+        <v>6415376</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122851012</v>
+        <v>122850835</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558276</v>
+        <v>558314</v>
       </c>
       <c r="R11" t="n">
-        <v>6415383</v>
+        <v>6415377</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122850740</v>
+        <v>122850901</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558324</v>
+        <v>558311</v>
       </c>
       <c r="R12" t="n">
-        <v>6415313</v>
+        <v>6415391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122851040</v>
+        <v>122850566</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558287</v>
+        <v>558328</v>
       </c>
       <c r="R13" t="n">
-        <v>6415363</v>
+        <v>6415288</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122851058</v>
+        <v>122850931</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558281</v>
+        <v>558298</v>
       </c>
       <c r="R14" t="n">
-        <v>6415357</v>
+        <v>6415413</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122850538</v>
+        <v>122850599</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558333</v>
+        <v>558331</v>
       </c>
       <c r="R15" t="n">
-        <v>6415279</v>
+        <v>6415292</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122851076</v>
+        <v>122851029</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558271</v>
+        <v>558287</v>
       </c>
       <c r="R16" t="n">
-        <v>6415361</v>
+        <v>6415378</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122850931</v>
+        <v>122851099</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>57851</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,35 +2352,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2387,13 +2392,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558298</v>
+        <v>558307</v>
       </c>
       <c r="R17" t="n">
-        <v>6415413</v>
+        <v>6415333</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,7 +2436,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2453,7 +2457,7 @@
         <v>122850746</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122850816</v>
+        <v>122850696</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>57634</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2573,35 +2577,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2609,13 +2617,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558317</v>
+        <v>558333</v>
       </c>
       <c r="R19" t="n">
-        <v>6415367</v>
+        <v>6415302</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2653,7 +2661,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122850920</v>
+        <v>122850918</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558291</v>
+        <v>558314</v>
       </c>
       <c r="R20" t="n">
-        <v>6415409</v>
+        <v>6415393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122850865</v>
+        <v>122850658</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>92247</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2795,35 +2802,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558306</v>
+        <v>558326</v>
       </c>
       <c r="R21" t="n">
-        <v>6415378</v>
+        <v>6415300</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2894,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122850991</v>
+        <v>122850937</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2942,10 +2948,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558288</v>
+        <v>558285</v>
       </c>
       <c r="R22" t="n">
-        <v>6415391</v>
+        <v>6415400</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122850696</v>
+        <v>122851040</v>
       </c>
       <c r="B23" t="n">
-        <v>57634</v>
+        <v>98379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3017,39 +3023,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3057,13 +3059,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558333</v>
+        <v>558287</v>
       </c>
       <c r="R23" t="n">
-        <v>6415302</v>
+        <v>6415363</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,6 +3103,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851054</v>
+        <v>122850974</v>
       </c>
       <c r="B24" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3167,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558287</v>
+        <v>558285</v>
       </c>
       <c r="R24" t="n">
-        <v>6415354</v>
+        <v>6415397</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3233,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122850715</v>
+        <v>122850816</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,10 +3281,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558327</v>
+        <v>558317</v>
       </c>
       <c r="R25" t="n">
-        <v>6415304</v>
+        <v>6415367</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851099</v>
+        <v>122851054</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3353,39 +3356,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3393,13 +3392,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558307</v>
+        <v>558287</v>
       </c>
       <c r="R26" t="n">
-        <v>6415333</v>
+        <v>6415354</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3437,6 +3436,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122850918</v>
+        <v>122851012</v>
       </c>
       <c r="B27" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558314</v>
+        <v>558276</v>
       </c>
       <c r="R27" t="n">
-        <v>6415393</v>
+        <v>6415383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850800</v>
+        <v>122850785</v>
       </c>
       <c r="B28" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558344</v>
+        <v>558330</v>
       </c>
       <c r="R28" t="n">
-        <v>6415332</v>
+        <v>6415337</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,10 +3677,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851029</v>
+        <v>122851065</v>
       </c>
       <c r="B29" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558287</v>
+        <v>558266</v>
       </c>
       <c r="R29" t="n">
-        <v>6415378</v>
+        <v>6415358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850913</v>
+        <v>122851058</v>
       </c>
       <c r="B30" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558297</v>
+        <v>558281</v>
       </c>
       <c r="R30" t="n">
-        <v>6415398</v>
+        <v>6415357</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850785</v>
+        <v>122850848</v>
       </c>
       <c r="B31" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558330</v>
+        <v>558303</v>
       </c>
       <c r="R31" t="n">
-        <v>6415337</v>
+        <v>6415374</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850848</v>
+        <v>122850740</v>
       </c>
       <c r="B32" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558303</v>
+        <v>558324</v>
       </c>
       <c r="R32" t="n">
-        <v>6415374</v>
+        <v>6415313</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4121,10 +4121,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850901</v>
+        <v>122850913</v>
       </c>
       <c r="B33" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558311</v>
+        <v>558297</v>
       </c>
       <c r="R33" t="n">
-        <v>6415391</v>
+        <v>6415398</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850974</v>
+        <v>122851076</v>
       </c>
       <c r="B34" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558285</v>
+        <v>558271</v>
       </c>
       <c r="R34" t="n">
-        <v>6415397</v>
+        <v>6415361</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850882</v>
+        <v>122851047</v>
       </c>
       <c r="B35" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558304</v>
+        <v>558301</v>
       </c>
       <c r="R35" t="n">
-        <v>6415376</v>
+        <v>6415402</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
